--- a/results/Int All Data -0.1/Rando_2_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_2_permute.xlsx
@@ -440,1507 +440,1507 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7488551132923571</v>
+        <v>0.7501083247378688</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7461991512009092</v>
+        <v>0.7486083128233634</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7458832952312313</v>
+        <v>0.7486083128233634</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7455380177278115</v>
+        <v>0.7496837793005651</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7446595053194619</v>
+        <v>0.7480060224177498</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7432183364724407</v>
+        <v>0.7483218783874277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7386480294623834</v>
+        <v>0.7505034486414303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7472451961443688</v>
+        <v>0.7505034486414303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7453896942932436</v>
+        <v>0.7501875926717525</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.750167167805353</v>
+        <v>0.749309080263403</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.74531042635936</v>
+        <v>0.7506223505422559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.74531042635936</v>
+        <v>0.7499906386029003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.74531042635936</v>
+        <v>0.7491811816952347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7418360106929038</v>
+        <v>0.7471875688427416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7418360106929038</v>
+        <v>0.7462003669667663</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7371275926814785</v>
+        <v>0.7399343097392085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7385981830622419</v>
+        <v>0.7421350890937535</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7554178173890504</v>
+        <v>0.7449087373201699</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7468897062077491</v>
+        <v>0.7452936487905318</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7336531770150225</v>
+        <v>0.7440992804125045</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7342158334536941</v>
+        <v>0.7446619368511762</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7319357861652653</v>
+        <v>0.7445136134166084</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7335150660136545</v>
+        <v>0.7527937083630588</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7338999774840163</v>
+        <v>0.7497540505671061</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.742072598728698</v>
+        <v>0.7497540505671061</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7442835905164428</v>
+        <v>0.7511952194141274</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.743967734546765</v>
+        <v>0.7450852665226226</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7434741336087773</v>
+        <v>0.7450852665226226</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7386083954954417</v>
+        <v>0.7437527871432275</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7355777343668316</v>
+        <v>0.7447003550522608</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7379958926566283</v>
+        <v>0.7447003550522608</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7372951252165887</v>
+        <v>0.739815407838383</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7372951252165887</v>
+        <v>0.735887025200881</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7406608514154189</v>
+        <v>0.7385519839596716</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7358539563695675</v>
+        <v>0.7529522442308263</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7219358688373436</v>
+        <v>0.7518665653204248</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7223207803077055</v>
+        <v>0.7474253726443929</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7223207803077055</v>
+        <v>0.7492808744955179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7192018545778691</v>
+        <v>0.7490340740265241</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7192018545778691</v>
+        <v>0.7461223147987397</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7199716775185927</v>
+        <v>0.7355098946320047</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7273054203218667</v>
+        <v>0.7399792930759217</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7228143812456932</v>
+        <v>0.7383117486263062</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7221136138056534</v>
+        <v>0.7393283720360235</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7246993046305603</v>
+        <v>0.7382426931256222</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7244128701946246</v>
+        <v>0.7382426931256222</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7247287261643025</v>
+        <v>0.7385879706290421</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7253898596374002</v>
+        <v>0.7391698361682562</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7253898596374002</v>
+        <v>0.7478859047510671</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7247875692317867</v>
+        <v>0.7454089033937861</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7086687023450178</v>
+        <v>0.7503436970078057</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6597085955132405</v>
+        <v>0.749435763065714</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6610704964263778</v>
+        <v>0.749435763065714</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6617712638664175</v>
+        <v>0.7463258340032204</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.65434804069606</v>
+        <v>0.747095656943944</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6533608388200847</v>
+        <v>0.7482503913550294</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6546242626987959</v>
+        <v>0.749197959264063</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6543774622298022</v>
+        <v>0.7437593522788558</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.65469331819948</v>
+        <v>0.7445508158518361</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6534989498214526</v>
+        <v>0.7418858570930456</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6534989498214526</v>
+        <v>0.7393385844692233</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6597151606488688</v>
+        <v>0.7392004734678554</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6436857741291835</v>
+        <v>0.7386083954954417</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6368252073974976</v>
+        <v>0.7381544285243957</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6289365890570374</v>
+        <v>0.7350841334288439</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.64617055638795</v>
+        <v>0.7351339798289855</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6377397064752176</v>
+        <v>0.7325176517044794</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6377102849414755</v>
+        <v>0.73180667183124</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6587843703086635</v>
+        <v>0.7293206738066164</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6415593996450937</v>
+        <v>0.7295278403086684</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6428228235238049</v>
+        <v>0.6968096358683997</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6392997772230643</v>
+        <v>0.6985666606850987</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.631698809084397</v>
+        <v>0.6983582784171896</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6307116072084217</v>
+        <v>0.6971230603063633</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6388650193525609</v>
+        <v>0.6913289633845365</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6404635083014925</v>
+        <v>0.6996204865300437</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6457141578851899</v>
+        <v>0.6927983379994427</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6212743463191717</v>
+        <v>0.694199872879522</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6212743463191717</v>
+        <v>0.6960169565295624</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6120940983321151</v>
+        <v>0.6915949729540727</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6058190444372147</v>
+        <v>0.6822868263988481</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6123625394333656</v>
+        <v>0.6820694474635963</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6109610045532863</v>
+        <v>0.6851691640928903</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6097270022083171</v>
+        <v>0.6801346776785875</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5929085836473657</v>
+        <v>0.6920183026255193</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5929085836473657</v>
+        <v>0.6988686569240053</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5870634245595402</v>
+        <v>0.6991436631608843</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5829969309206703</v>
+        <v>0.7083905351169104</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5837144759295381</v>
+        <v>0.7052716093870741</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5887285374774415</v>
+        <v>0.7138789885022592</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5888654327129523</v>
+        <v>0.7117076306814563</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5784716072473262</v>
+        <v>0.7178878548395019</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5746813356111923</v>
+        <v>0.7153610070820793</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5754511585519159</v>
+        <v>0.7144428607067879</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5736250782345329</v>
+        <v>0.711135977575442</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5615829174198336</v>
+        <v>0.7262394368183505</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5615138619191496</v>
+        <v>0.7247292124706453</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.553617462677204</v>
+        <v>0.7205540293641496</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5538936846799399</v>
+        <v>0.7026013012585122</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5547721970882894</v>
+        <v>0.6903711830423034</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5564205324373626</v>
+        <v>0.6903711830423034</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5578617012843837</v>
+        <v>0.6958596364276519</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5509525039184133</v>
+        <v>0.6954747249572901</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5493041685693402</v>
+        <v>0.6647153624660012</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5440330941192433</v>
+        <v>0.6588624224766901</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5340752422899777</v>
+        <v>0.6368701907342107</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5492849594687979</v>
+        <v>0.6351540156503107</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5507555498495611</v>
+        <v>0.6367729294656417</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5539038971131396</v>
+        <v>0.6115122327929011</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5638143340739779</v>
+        <v>0.6033306148808768</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5610304734143617</v>
+        <v>0.6034393043485027</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5514064708894592</v>
+        <v>0.597921429429412</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5546737200538633</v>
+        <v>0.6009010283920232</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5490970020672883</v>
+        <v>0.6019597173003968</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5368770962842792</v>
+        <v>0.6008446168562532</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5220714996763631</v>
+        <v>0.6008446168562532</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5115191383429695</v>
+        <v>0.5968087605169825</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5130984181913586</v>
+        <v>0.5969570839515502</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5118349943126473</v>
+        <v>0.5974621130885949</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5069296222323698</v>
+        <v>0.5847731648379118</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5064360212943821</v>
+        <v>0.5824240620487989</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5069986777330537</v>
+        <v>0.5794318191212736</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5069986777330537</v>
+        <v>0.5440253132177577</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5053107084170388</v>
+        <v>0.5416467888949028</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5031789845631778</v>
+        <v>0.5385585004646657</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.502794073092816</v>
+        <v>0.5358845450385324</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5010472607093167</v>
+        <v>0.5192720772137759</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4960728331283552</v>
+        <v>0.5243948282293051</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4990434354236239</v>
+        <v>0.5214626441351212</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4891738481955846</v>
+        <v>0.5214626441351212</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4964475321655173</v>
+        <v>0.5174856308633348</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.496526800099401</v>
+        <v>0.5149077209399134</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.492499940427473</v>
+        <v>0.5147299759716036</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4928848518978348</v>
+        <v>0.5130996339572157</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4928848518978348</v>
+        <v>0.5127147224868539</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4949475202510119</v>
+        <v>0.5123592325502342</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4954014872220577</v>
+        <v>0.5125369775185441</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4957173431917355</v>
+        <v>0.5158528573172327</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4974347340414926</v>
+        <v>0.5071175796338794</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4957863986924195</v>
+        <v>0.5052914993164964</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4960229867282136</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4981841321158168</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4966444862343695</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4987173670207463</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4987173670207463</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4987173670207463</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4990626445241663</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4998324674648899</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4998324674648899</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.499723777997264</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4997928334979481</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.499861888998632</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4996150885296382</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4996150885296382</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4996150885296382</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
